--- a/data/trans_orig/P34B02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P34B02-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población realiza gimnasia suave juegos que requieren poco esfuerzo y similares</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población realiza gimnasia suave como juegos que requieren poco esfuerzo y similares (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -682,42 +682,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,63</t>
+          <t>0,36; 0,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,17</t>
+          <t>0,83; 1,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,44</t>
+          <t>0,18; 0,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,67</t>
+          <t>0,37; 0,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,33</t>
+          <t>0,99; 1,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,45</t>
+          <t>0,26; 0,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,59</t>
+          <t>0,4; 0,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,2</t>
+          <t>0,94; 1,18</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,43</t>
+          <t>0,21; 0,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,76</t>
+          <t>0,43; 0,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,23</t>
+          <t>0,84; 1,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,45</t>
+          <t>0,18; 0,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,59</t>
+          <t>0,27; 0,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,14</t>
+          <t>0,85; 1,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -897,37 +897,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,46</t>
+          <t>0,24; 0,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,51</t>
+          <t>0,29; 0,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,85</t>
+          <t>0,2; 0,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,42</t>
+          <t>0,16; 0,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,63</t>
+          <t>0,26; 0,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,86</t>
+          <t>0,44; 0,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,4</t>
+          <t>0,24; 0,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,79</t>
+          <t>0,25; 0,79</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,31</t>
+          <t>0,18; 0,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,43</t>
+          <t>0,29; 0,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,01</t>
+          <t>0,75; 1,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,37</t>
+          <t>0,22; 0,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,75</t>
+          <t>0,27; 0,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,39</t>
+          <t>0,28; 0,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,5</t>
+          <t>0,25; 0,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,42</t>
+          <t>0,23; 0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,39</t>
+          <t>0,22; 0,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,64</t>
+          <t>0,44; 0,65</t>
         </is>
       </c>
     </row>
@@ -1227,32 +1227,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,66</t>
+          <t>0,34; 0,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,88</t>
+          <t>0,46; 0,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,02</t>
+          <t>1,19; 2,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,3</t>
+          <t>0,19; 0,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,25</t>
+          <t>0,14; 0,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,59</t>
+          <t>0,41; 0,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,36</t>
+          <t>0,23; 0,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,89</t>
+          <t>0,62; 0,89</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,37</t>
+          <t>0,28; 0,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,97</t>
+          <t>0,64; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,26</t>
+          <t>0,19; 0,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,81</t>
+          <t>0,66; 0,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P34B02-Clase-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,03</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,54</t>
+          <t>0,29; 0,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,66</t>
+          <t>0,36; 0,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,18</t>
+          <t>0,8; 1,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,46</t>
+          <t>0,18; 0,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,66</t>
+          <t>0,37; 0,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,35</t>
+          <t>0,96; 1,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,44</t>
+          <t>0,27; 0,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,61</t>
+          <t>0,39; 0,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,18</t>
+          <t>0,92; 1,16</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,41</t>
+          <t>0,21; 0,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,75</t>
+          <t>0,44; 0,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,23</t>
+          <t>0,81; 1,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -807,27 +807,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,56</t>
+          <t>0,29; 0,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,13</t>
+          <t>0,81; 1,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,38</t>
+          <t>0,22; 0,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,62</t>
+          <t>0,41; 0,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,13</t>
+          <t>0,86; 1,08</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,76</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,45</t>
+          <t>0,25; 0,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,51</t>
+          <t>0,29; 0,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,86</t>
+          <t>0,66; 1,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,41</t>
+          <t>0,15; 0,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,65</t>
+          <t>0,26; 0,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,87</t>
+          <t>0,44; 0,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,4</t>
+          <t>0,24; 0,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,5</t>
+          <t>0,3; 0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,79</t>
+          <t>0,63; 0,92</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,8</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,31</t>
+          <t>0,19; 0,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,04</t>
+          <t>0,75; 0,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,36</t>
+          <t>0,23; 0,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,75</t>
+          <t>0,61; 0,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,28</t>
+          <t>0,19; 0,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,84</t>
+          <t>0,71; 0,88</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,64</t>
         </is>
       </c>
     </row>
@@ -1117,32 +1117,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,49</t>
+          <t>0,24; 0,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,43</t>
+          <t>0,24; 0,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,95</t>
+          <t>0,64; 0,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,17</t>
+          <t>0,08; 0,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,39</t>
+          <t>0,21; 0,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,53</t>
+          <t>0,46; 0,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1157,14 +1157,14 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,65</t>
+          <t>0,55; 0,73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,59</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,75</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1227,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,63</t>
+          <t>0,33; 0,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,89</t>
+          <t>0,48; 0,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,04</t>
+          <t>1,34; 2,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,25</t>
+          <t>0,15; 0,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,59</t>
+          <t>0,39; 0,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,35</t>
+          <t>0,24; 0,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,89</t>
+          <t>0,64; 0,88</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,81</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,97</t>
+          <t>0,86; 1,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,7</t>
+          <t>0,65; 0,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,82</t>
+          <t>0,77; 0,85</t>
         </is>
       </c>
     </row>
